--- a/databases/tabela_contingencia_ans.xlsx
+++ b/databases/tabela_contingencia_ans.xlsx
@@ -382,14 +382,20 @@
           <t>Highest rates</t>
         </is>
       </c>
-      <c r="B2">
-        <v>554</v>
-      </c>
-      <c r="C2">
-        <v>124</v>
-      </c>
-      <c r="D2">
-        <v>616</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>151 (2.7%)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>177 (3.2%)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>66 (1.2%)</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -398,14 +404,20 @@
           <t>Intermediary rates</t>
         </is>
       </c>
-      <c r="B3">
-        <v>3332</v>
-      </c>
-      <c r="C3">
-        <v>73</v>
-      </c>
-      <c r="D3">
-        <v>476</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>140 (2.5%)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>626 (11.2%)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>528 (9.5%)</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -414,14 +426,20 @@
           <t>Lowest rates</t>
         </is>
       </c>
-      <c r="B4">
-        <v>69</v>
-      </c>
-      <c r="C4">
-        <v>132</v>
-      </c>
-      <c r="D4">
-        <v>193</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>84 (1.5%)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>509 (9.1%)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3288 (59%)</t>
+        </is>
       </c>
     </row>
   </sheetData>
